--- a/public/templates/people-import-template.xlsx
+++ b/public/templates/people-import-template.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:T5"/>
   <cols>
     <col min="1" max="1" width="18.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -419,6 +419,7 @@
     <col min="17" max="17" width="18.83203125" customWidth="1"/>
     <col min="18" max="18" width="18.83203125" customWidth="1"/>
     <col min="19" max="19" width="18.83203125" customWidth="1"/>
+    <col min="20" max="20" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,6 +480,9 @@
       <c r="S1" t="str">
         <v>group_id</v>
       </c>
+      <c r="T1" t="str">
+        <v>accommodation_funding_type</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -538,6 +542,9 @@
       <c r="S2" t="str">
         <v>Smith Family</v>
       </c>
+      <c r="T2" t="str">
+        <v>forum_covered</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -597,6 +604,9 @@
       <c r="S3" t="str">
         <v/>
       </c>
+      <c r="T3" t="str">
+        <v>self_funded</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -656,6 +666,9 @@
       <c r="S4" t="str">
         <v/>
       </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -715,17 +728,20 @@
       <c r="S5" t="str">
         <v/>
       </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <cols>
     <col min="1" max="1" width="22.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -1013,34 +1029,48 @@
         <v>Any text</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>NOTES:</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>accommodation_funding_type</v>
+      </c>
+      <c r="B21" t="str">
+        <v>No</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Who funds the accommodation</v>
+      </c>
+      <c r="D21" t="str">
+        <v>self_funded or forum_covered</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>- Rows 3 and 4 in the People sheet contain intentional errors as examples.</v>
+        <v>NOTES:</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>- Remove all example rows before importing your data.</v>
+        <v>- Rows 3 and 4 in the People sheet contain intentional errors as examples.</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>- If a person_id already exists in the database, the row will UPDATE the existing record.</v>
+        <v>- Remove all example rows before importing your data.</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
+        <v>- If a person_id already exists in the database, the row will UPDATE the existing record.</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
         <v>- Dates must be in YYYY-MM-DD format (e.g. 2026-04-10).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D27"/>
   </ignoredErrors>
 </worksheet>
 </file>